--- a/stories/arbres/ATOM-SOC.ARG.002-06.xlsx
+++ b/stories/arbres/ATOM-SOC.ARG.002-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Fleur est à la papeterie avec maman. Elle voit un crayon bleu. Elle a envie. L'argent se range. Fleur ne le prend pas. Elle va demander à maman. Maman, c'est l'adulte. Fleur dit : s'il te plaît, ce crayon ? Maman écoute. Elle dit oui. Elle paie. Fleur dit merci. On demande à l'adulte.</t>
+          <t>Fleur est à la papeterie avec maman. Elle voit un crayon bleu. Elle a envie. L'argent se range. Fleur ne le prend pas. Elle va demander à maman. Maman, c'est l'adulte. S'il te plaît, ce crayon ? Maman écoute. Elle dit oui. Elle paie. Fleur dit merci. On demande à l'adulte.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,13 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Fleur est à la papeterie avec maman. Elle voit un crayon bleu. Elle a envie. L'argent se range. Fleur ne le prend pas. Elle va demander à maman. Maman, c'est l'adulte.
+enfant-m|S'il te plaît, ce crayon ? Maman écoute. Elle dit oui. Elle paie.
+narrateur|Fleur dit merci. On demande à l'adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1488,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Fleur veut un crayon. Que fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1661,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Fleur a demandé à l'adulte. Maman a écouté.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1824,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Elles sortent. Fleur tient le crayon.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1991,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2031,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SOC.ARG.002-06.xlsx
+++ b/stories/arbres/ATOM-SOC.ARG.002-06.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1312,6 +1317,7 @@
 narrateur|Fleur dit merci. On demande à l'adulte.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1495,6 +1501,7 @@
           <t>narrateur|Fleur veut un crayon. Que fait-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1666,6 +1673,7 @@
           <t>narrateur|Fleur a demandé à l'adulte. Maman a écouté.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1829,6 +1837,7 @@
           <t>narrateur|Elles sortent. Fleur tient le crayon.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1996,6 +2005,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2014,7 +2024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2038,6 +2048,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2239,6 +2263,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SOC.ARG.002-06.xlsx
+++ b/stories/arbres/ATOM-SOC.ARG.002-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Fleur demande pour un crayon</t>
+          <t>Le crayon jaune de Chouchou</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Chouchou veut un crayon jaune. Elle tend la main vers le pot. Maman attend. Chouchou demande. Le crayon laisse un trait.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Fleur est à la papeterie avec maman. Elle voit un crayon bleu. Elle a envie. L'argent se range. Fleur ne le prend pas. Elle va demander à maman. Maman, c'est l'adulte. S'il te plaît, ce crayon ? Maman écoute. Elle dit oui. Elle paie. Fleur dit merci. On demande à l'adulte.</t>
+          <t>Un pot de verre tient des crayons jaunes. Le verre fait un rond de soleil. Ça sent le papier et le bois. Des feuilles blanches attendent en pile. Maman pousse la porte. Un tapis racle sous les chaussures. Les crayons ! Oui. Ils sont dans le pot. Chouchou marche entre deux rayons. Le papier craque un peu sous le doigt. Une gomme blanche attend plus loin. Chouchou ne la regarde pas. Un crayon bleu est trop loin. Je veux le jaune. Le jaune du pot ? Oui. En ce moment, Chouchou s'approche du verre. Un crayon jaune dépasse les autres. La mine est nette, encore pointue. Celui-là. Il est jaune. Chouchou tend la main. Ses doigts touchent le bois. Maman n'ouvre pas le sac. Chouchou. Tu me demandes ? La main s'arrête sur le bord du pot. Oh. Chouchou rentre les doigts. On achète si tu demandes. Tu te souviens ? Je peux demander. Tu me dis s'il te plaît ? Oui, maman. Le pot de verre reste plein. Le rond de soleil a bougé.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Fleur est à la papeterie avec maman. Elle voit un crayon bleu. Elle a envie. L'argent se range. Fleur ne le prend pas. Elle va &lt;emphasis level="moderate"&gt;demander&lt;/emphasis&gt; à maman. Maman, c'est l'adulte. Fleur dit : s'il te plaît, ce crayon ? Maman écoute. Elle dit oui. Elle paie. Fleur dit merci. On demande à l'adulte.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Un pot de verre tient des crayons jaunes. Le verre fait un rond de soleil. Ça sent le papier et le bois. Des feuilles blanches attendent en pile. Maman pousse la porte. Un tapis racle sous les chaussures. Les crayons ! Oui. Ils sont dans le pot. Chouchou marche entre deux rayons. Le papier craque un peu sous le doigt. Une gomme blanche attend plus loin. Chouchou ne la regarde pas. Un crayon bleu est trop loin. Je veux le jaune. Le jaune du pot ? Oui. En ce moment, Chouchou s'approche du verre. Un crayon jaune dépasse les autres. La mine est nette, encore pointue. Celui-là. Il est jaune. Chouchou tend la main. Ses doigts touchent le bois. Maman n'ouvre pas le sac. Chouchou. Tu me demandes ? La main s'arrête sur le bord du pot. Oh. Chouchou rentre les doigts. On achète si tu demandes. Tu te souviens ? Je peux demander. Tu me dis s'il te plaît ? Oui, maman. Le pot de verre reste plein. Le rond de soleil a bougé.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1240,7 +1252,7 @@
         <v>0.92</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,12 +1324,45 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Fleur est à la papeterie avec maman. Elle voit un crayon bleu. Elle a envie. L'argent se range. Fleur ne le prend pas. Elle va demander à maman. Maman, c'est l'adulte.
-enfant-m|S'il te plaît, ce crayon ? Maman écoute. Elle dit oui. Elle paie.
-narrateur|Fleur dit merci. On demande à l'adulte.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Un pot de verre tient des crayons jaunes.
+narrateur|Le verre fait un rond de soleil.
+narrateur|Ça sent le papier et le bois.
+narrateur|Des feuilles blanches attendent en pile.
+narrateur|Maman pousse la porte.
+narrateur|Un tapis racle sous les chaussures.
+enfant-f|Les crayons !
+maman|Oui.
+maman|Ils sont dans le pot.
+narrateur|Chouchou marche entre deux rayons.
+narrateur|Le papier craque un peu sous le doigt.
+narrateur|Une gomme blanche attend plus loin.
+narrateur|Chouchou ne la regarde pas.
+narrateur|Un crayon bleu est trop loin.
+enfant-f|Je veux le jaune.
+maman|Le jaune du pot ?
+enfant-f|Oui.
+narrateur|En ce moment, Chouchou s'approche du verre.
+narrateur|Un crayon jaune dépasse les autres.
+narrateur|La mine est nette, encore pointue.
+enfant-f|Celui-là.
+enfant-f|Il est jaune.
+narrateur|Chouchou tend la main.
+narrateur|Ses doigts touchent le bois.
+narrateur|Maman n'ouvre pas le sac.
+maman|Chouchou.
+maman|Tu me demandes ?
+narrateur|La main s'arrête sur le bord du pot.
+enfant-f|Oh.
+narrateur|Chouchou rentre les doigts.
+maman|On achète si tu demandes.
+maman|Tu te souviens ?
+enfant-f|Je peux demander.
+maman|Tu me dis s'il te plaît ?
+enfant-f|Oui, maman.
+narrateur|Le pot de verre reste plein.
+narrateur|Le rond de soleil a bougé.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1342,12 +1387,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Fleur veut un crayon. Que fait-elle ?</t>
+          <t>Chouchou veut le crayon jaune. Que fait-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Fleur veut un crayon. Que fait-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Chouchou veut le crayon jaune. Que fait-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1362,7 +1407,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>demander | maman | l'adulte</t>
+          <t>demander | elle demande | à maman | s'il te plaît</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1377,7 +1422,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>L'argent se range. Elle le dit à qui ?</t>
+          <t>Elle demande à maman. Que fait Chouchou ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1426,7 +1471,7 @@
         <v>0.86</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1498,10 +1543,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Fleur veut un crayon. Que fait-elle ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Chouchou veut le crayon jaune.
+narrateur|Que fait-elle ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1526,12 +1571,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Fleur a demandé à l'adulte. Maman a écouté.</t>
+          <t>Maman, s'il te plaît. Je peux avoir le crayon ? Oui. Merci, Chouchou. Tu as demandé. Maman ouvre le petit sac. Elle pose l'argent sur le bois. On lui tend le crayon jaune. Chouchou le prend. Le bois est hexagonal, un peu froid. Il est à moi. Oui. Parce que tu as demandé. Tu le tiens bien ? Oui, maman. Le pot de verre a un crayon en moins. Les autres crayons se touchent.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Fleur a demandé à l'&lt;emphasis level="moderate"&gt;adulte&lt;/emphasis&gt;. Maman a écouté.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Maman, s'il te plaît. Je peux avoir le crayon ? Oui. Merci, Chouchou. Tu as demandé. Maman ouvre le petit sac. Elle pose l'argent sur le bois. On lui tend le crayon jaune. Chouchou le prend. Le bois est hexagonal, un peu froid. Il est à moi. Oui. Parce que tu as demandé. Tu le tiens bien ? Oui, maman. Le pot de verre a un crayon en moins. Les autres crayons se touchent.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1594,7 +1639,7 @@
         <v>0.92</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1670,10 +1715,25 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Fleur a demandé à l'adulte. Maman a écouté.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>enfant-f|Maman, s'il te plaît.
+enfant-f|Je peux avoir le crayon ?
+maman|Oui.
+maman|Merci, Chouchou.
+maman|Tu as demandé.
+narrateur|Maman ouvre le petit sac.
+narrateur|Elle pose l'argent sur le bois.
+narrateur|On lui tend le crayon jaune.
+narrateur|Chouchou le prend.
+narrateur|Le bois est hexagonal, un peu froid.
+enfant-f|Il est à moi.
+maman|Oui.
+maman|Parce que tu as demandé.
+maman|Tu le tiens bien ?
+enfant-f|Oui, maman.
+narrateur|Le pot de verre a un crayon en moins.
+narrateur|Les autres crayons se touchent.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1698,12 +1758,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Elles sortent. Fleur tient le crayon.</t>
+          <t>Elles sortent. La rue sent le papier, encore un peu. Chouchou marche avec le crayon. La mine pointe vers le ciel. On dessinera à la maison ? Oui. Un soleil. Tu as demandé avant d'acheter. Bravo. Le crayon tape un peu sa poche. Chouchou le sent, tout près du nez. Ça sent le bois neuf. Tu le mets dans ta poche ? Pas encore. Il est jaune.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Elles sortent. Fleur tient le crayon.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Elles sortent. La rue sent le papier, encore un peu. Chouchou marche avec le crayon. La mine pointe vers le ciel. On dessinera à la maison ? Oui. Un soleil. Tu as demandé avant d'acheter. Bravo. Le crayon tape un peu sa poche. Chouchou le sent, tout près du nez. Ça sent le bois neuf. Tu le mets dans ta poche ? Pas encore. Il est jaune.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1766,7 +1826,7 @@
         <v>0.92</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1834,10 +1894,23 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Elles sortent. Fleur tient le crayon.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Elles sortent.
+narrateur|La rue sent le papier, encore un peu.
+narrateur|Chouchou marche avec le crayon.
+narrateur|La mine pointe vers le ciel.
+maman|On dessinera à la maison ?
+enfant-f|Oui.
+enfant-f|Un soleil.
+maman|Tu as demandé avant d'acheter.
+maman|Bravo.
+narrateur|Le crayon tape un peu sa poche.
+narrateur|Chouchou le sent, tout près du nez.
+narrateur|Ça sent le bois neuf.
+maman|Tu le mets dans ta poche ?
+enfant-f|Pas encore.
+enfant-f|Il est jaune.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1862,12 +1935,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>À la table, Chouchou pose une feuille. Elle trace un trait jaune. Le trait est vif, tout droit. C'est le soleil. Oui. Tu l'as dans les mains. Chouchou tient encore le crayon. Elle ajoute un petit rond. Il chauffe. Le soleil, oui. Le crayon jaune laisse un trait sur le papier.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>À la table, Chouchou pose une feuille. Elle trace un trait jaune. Le trait est vif, tout droit. C'est le soleil. Oui. Tu l'as dans les mains. Chouchou tient encore le crayon. Elle ajoute un petit rond. Il chauffe. Le soleil, oui. Le crayon jaune laisse un trait sur le papier.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1923,14 +1996,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.88</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2002,10 +2075,19 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|À la table, Chouchou pose une feuille.
+narrateur|Elle trace un trait jaune.
+narrateur|Le trait est vif, tout droit.
+enfant-f|C'est le soleil.
+maman|Oui.
+maman|Tu l'as dans les mains.
+narrateur|Chouchou tient encore le crayon.
+narrateur|Elle ajoute un petit rond.
+enfant-f|Il chauffe.
+maman|Le soleil, oui.
+narrateur|Le crayon jaune laisse un trait sur le papier.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2024,7 +2106,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2062,6 +2144,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SOC.ARG.002-06.xlsx
+++ b/stories/arbres/ATOM-SOC.ARG.002-06.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>papeterie</t>
+          <t>papeterie, pot de verre, rayons de papier</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Fleur, maman</t>
+          <t>Chouchou, maman</t>
         </is>
       </c>
     </row>
